--- a/encomendas_a_editora/encomenda_editora_2026-06-23.xlsx
+++ b/encomendas_a_editora/encomenda_editora_2026-06-23.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ISBN do manual</t>
   </si>
@@ -32,10 +32,16 @@
     <t>Tipo do manual</t>
   </si>
   <si>
+    <t>ingles</t>
+  </si>
+  <si>
+    <t>Grupo Penguin X</t>
+  </si>
+  <si>
+    <t>Livro de Fichas</t>
+  </si>
+  <si>
     <t>area integração</t>
-  </si>
-  <si>
-    <t>Grupo Penguin X</t>
   </si>
   <si>
     <t>Manual</t>
@@ -97,7 +103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -105,7 +111,7 @@
     <col min="4" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -133,46 +139,69 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1234567891</v>
+        <v>1234567896</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>10.25</v>
+        <v>112.50</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
-        <v>4444444444444</v>
+      <c r="A3">
+        <v>1234567891</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="D3"/>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10.25</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2">
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>4444444444444</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2">
         <v>12.00</v>
       </c>
-      <c r="G3" t="s">
-        <v>9</v>
+      <c r="G4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
